--- a/artfynd/A 64813-2023 artfynd.xlsx
+++ b/artfynd/A 64813-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119517088</v>
+        <v>119517083</v>
       </c>
       <c r="B2" t="n">
-        <v>8421</v>
+        <v>5169</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,7 +714,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521512</v>
+        <v>521546</v>
       </c>
       <c r="R2" t="n">
-        <v>6540033</v>
+        <v>6539985</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119517083</v>
+        <v>119517088</v>
       </c>
       <c r="B3" t="n">
-        <v>5169</v>
+        <v>8421</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,7 +835,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521546</v>
+        <v>521512</v>
       </c>
       <c r="R3" t="n">
-        <v>6539985</v>
+        <v>6540033</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>

--- a/artfynd/A 64813-2023 artfynd.xlsx
+++ b/artfynd/A 64813-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>119517083</v>
       </c>
       <c r="B2" t="n">
-        <v>5169</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,12 +794,7 @@
         <v>119517088</v>
       </c>
       <c r="B3" t="n">
-        <v>8421</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 64813-2023 artfynd.xlsx
+++ b/artfynd/A 64813-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119517083</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,8 +914,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119517088</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>